--- a/test_calls.xlsx
+++ b/test_calls.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -61,7 +58,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,17 +424,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -447,30 +435,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>dietician_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>patient_id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>patient_name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>appointment_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>call_datetime</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>recording_url</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>call_duration_seconds</t>
         </is>
@@ -479,106 +472,85 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dr. Rajesh</t>
+          <t>Dr. Rajesh Kumar</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>DTN001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>PAT001</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Amit Kumar</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Rajiv Singh</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>APT001</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2024-01-15 10:30:00</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://example.com/call1.wav</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>900</v>
+          <t>2024-01-15 09:30:00</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>test_call_001.wav</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1245</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dr. Rajesh</t>
+          <t>Dr. Priya Sharma</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>DTN002</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>PAT002</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Priya Singh</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Meera Patel</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>APT002</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2024-01-15 11:00:00</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://example.com/call2.wav</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Dr. Neha</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>PAT003</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Raj Patel</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>APT003</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2024-01-15 14:30:00</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://example.com/call3.wav</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>800</v>
+          <t>2024-01-15 10:15:00</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>test_call_002.wav</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>892</t>
+        </is>
       </c>
     </row>
   </sheetData>
